--- a/FedMilLiPst1T.xlsx
+++ b/FedMilLiPst1T.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\FedGMil\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96347258-B64A-452F-9A2B-2B876917F25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A04C7E-6A02-4588-A10F-9F04D290389B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D799E344-D4C4-4034-8146-966A8431B7C5}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>Command Tier</t>
   </si>
   <si>
-    <t>Federal Agency / Branch</t>
-  </si>
-  <si>
     <t>Total Transaction Logs</t>
   </si>
   <si>
@@ -86,6 +83,9 @@
   </si>
   <si>
     <t>US Army</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
@@ -639,7 +639,7 @@
   <autoFilter ref="A1:H11" xr:uid="{BBBDF303-9FB4-4BBC-AE7F-CD51C53CCAB1}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D7097429-00C7-4160-AB65-543812BAE757}" name="Command Tier"/>
-    <tableColumn id="2" xr3:uid="{4F65FDD3-B3FE-4846-8FD6-432A3C1744B1}" name="Federal Agency / Branch"/>
+    <tableColumn id="2" xr3:uid="{4F65FDD3-B3FE-4846-8FD6-432A3C1744B1}" name="Agency"/>
     <tableColumn id="3" xr3:uid="{84CE297F-95BC-4AE4-8B0B-4B6D8B45A9E1}" name="Total Transaction Logs"/>
     <tableColumn id="4" xr3:uid="{0C77066A-2E50-48CF-97F1-43C536C4BED4}" name="Active Buffer Units"/>
     <tableColumn id="5" xr3:uid="{AD63D85F-EF81-41A3-BCAE-EF29437E19B1}" name="Safety Threshold Limit"/>
@@ -986,33 +986,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
       </c>
       <c r="C2">
         <v>1154</v>
@@ -1030,15 +1030,15 @@
         <v>10547</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>1154</v>
@@ -1056,15 +1056,15 @@
         <v>9863</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
       </c>
       <c r="C4">
         <v>1154</v>
@@ -1082,15 +1082,15 @@
         <v>9179</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>1154</v>
@@ -1108,15 +1108,15 @@
         <v>8495</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>1154</v>
@@ -1134,15 +1134,15 @@
         <v>7811</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
       </c>
       <c r="C7">
         <v>1153</v>
@@ -1160,15 +1160,15 @@
         <v>7120</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>1154</v>
@@ -1186,15 +1186,15 @@
         <v>6241</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>1154</v>
@@ -1212,15 +1212,15 @@
         <v>5899</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>1154</v>
@@ -1238,15 +1238,15 @@
         <v>5215</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>1153</v>
@@ -1264,7 +1264,7 @@
         <v>2489</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
